--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592965.5210136648</v>
+        <v>592966</v>
       </c>
       <c r="R2" t="n">
-        <v>6417737.290081374</v>
+        <v>6417737</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592865.3860568615</v>
+        <v>592865</v>
       </c>
       <c r="R3" t="n">
-        <v>6417736.032889076</v>
+        <v>6417736</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,12 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592865.3860568615</v>
+        <v>592865</v>
       </c>
       <c r="R4" t="n">
-        <v>6417736.032889076</v>
+        <v>6417736</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -995,19 +960,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109293</v>
+        <v>109298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109298</v>
+        <v>109306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>74128624</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>98573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74573427</v>
       </c>
       <c r="B3" t="n">
-        <v>109306</v>
+        <v>109316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>74969372</v>
       </c>
       <c r="B4" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>129118244</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,6 +3344,435 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129278899</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>593282</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6417172</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129278881</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96265</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>592953</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6417881</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129279083</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>592964</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6417600</v>
+      </c>
+      <c r="S27" t="n">
+        <v>150</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129278856</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>592957</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6417858</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>129118244</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>129279083</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>129278856</v>
       </c>
       <c r="B28" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3774,6 +3774,244 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129350271</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>593357</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6417338</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129350252</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92177</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>593351</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6417345</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3456,38 +3456,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129278881</v>
+        <v>129279083</v>
       </c>
       <c r="B26" t="n">
-        <v>96306</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3495,13 +3503,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592953</v>
+        <v>592964</v>
       </c>
       <c r="R26" t="n">
-        <v>6417881</v>
+        <v>6417600</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3539,7 +3547,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,46 +3565,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129279083</v>
+        <v>129278881</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>96308</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3605,13 +3604,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592964</v>
+        <v>592953</v>
       </c>
       <c r="R27" t="n">
-        <v>6417600</v>
+        <v>6417881</v>
       </c>
       <c r="S27" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3649,6 +3648,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3456,46 +3456,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129279083</v>
+        <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>96312</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3503,13 +3495,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592964</v>
+        <v>592953</v>
       </c>
       <c r="R26" t="n">
-        <v>6417600</v>
+        <v>6417881</v>
       </c>
       <c r="S26" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3547,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3565,38 +3558,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129278881</v>
+        <v>129279083</v>
       </c>
       <c r="B27" t="n">
-        <v>96308</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3604,13 +3605,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592953</v>
+        <v>592964</v>
       </c>
       <c r="R27" t="n">
-        <v>6417881</v>
+        <v>6417600</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3648,7 +3649,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>129118195</v>
       </c>
       <c r="B22" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>129118299</v>
       </c>
       <c r="B23" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3456,38 +3456,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129278881</v>
+        <v>129279083</v>
       </c>
       <c r="B26" t="n">
-        <v>96323</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3495,13 +3503,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592953</v>
+        <v>592964</v>
       </c>
       <c r="R26" t="n">
-        <v>6417881</v>
+        <v>6417600</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3539,7 +3547,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,46 +3565,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129279083</v>
+        <v>129278881</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>96323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3605,13 +3604,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592964</v>
+        <v>592953</v>
       </c>
       <c r="R27" t="n">
-        <v>6417600</v>
+        <v>6417881</v>
       </c>
       <c r="S27" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3649,6 +3648,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3456,46 +3456,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129279083</v>
+        <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>96323</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3503,13 +3495,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592964</v>
+        <v>592953</v>
       </c>
       <c r="R26" t="n">
-        <v>6417600</v>
+        <v>6417881</v>
       </c>
       <c r="S26" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3547,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3565,38 +3558,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129278881</v>
+        <v>129279083</v>
       </c>
       <c r="B27" t="n">
-        <v>96323</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3604,13 +3605,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592953</v>
+        <v>592964</v>
       </c>
       <c r="R27" t="n">
-        <v>6417881</v>
+        <v>6417600</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3648,7 +3649,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>129279083</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>129278856</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>129350271</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3456,38 +3456,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129278881</v>
+        <v>129279083</v>
       </c>
       <c r="B26" t="n">
-        <v>96352</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3495,13 +3503,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592953</v>
+        <v>592964</v>
       </c>
       <c r="R26" t="n">
-        <v>6417881</v>
+        <v>6417600</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3539,7 +3547,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,46 +3565,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129279083</v>
+        <v>129278881</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>96352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3605,13 +3604,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592964</v>
+        <v>592953</v>
       </c>
       <c r="R27" t="n">
-        <v>6417600</v>
+        <v>6417881</v>
       </c>
       <c r="S27" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3649,6 +3648,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3456,46 +3456,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129279083</v>
+        <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>96364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3503,13 +3495,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592964</v>
+        <v>592953</v>
       </c>
       <c r="R26" t="n">
-        <v>6417600</v>
+        <v>6417881</v>
       </c>
       <c r="S26" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3547,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3565,38 +3558,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129278881</v>
+        <v>129279083</v>
       </c>
       <c r="B27" t="n">
-        <v>96352</v>
+        <v>57732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3604,13 +3605,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592953</v>
+        <v>592964</v>
       </c>
       <c r="R27" t="n">
-        <v>6417881</v>
+        <v>6417600</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3648,7 +3649,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>129278856</v>
       </c>
       <c r="B28" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>129350271</v>
       </c>
       <c r="B29" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3350,7 +3350,7 @@
         <v>129278899</v>
       </c>
       <c r="B25" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>129278881</v>
       </c>
       <c r="B26" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>129279083</v>
       </c>
       <c r="B27" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>129278856</v>
       </c>
       <c r="B28" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>129350271</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -3898,7 +3898,7 @@
         <v>129350252</v>
       </c>
       <c r="B30" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4012,6 +4012,532 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130076638</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91631</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>593208</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6417302</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130076628</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>593090</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6417440</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130076603</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>593101</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6417299</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130076614</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91631</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>593100</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6417400</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130076611</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 64440, Vinö, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>593100</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6417400</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -4017,7 +4017,7 @@
         <v>130076638</v>
       </c>
       <c r="B31" t="n">
-        <v>91631</v>
+        <v>91644</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>130076628</v>
       </c>
       <c r="B32" t="n">
-        <v>96398</v>
+        <v>96411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>130076603</v>
       </c>
       <c r="B33" t="n">
-        <v>96398</v>
+        <v>96411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>130076614</v>
       </c>
       <c r="B34" t="n">
-        <v>91631</v>
+        <v>91644</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>130076611</v>
       </c>
       <c r="B35" t="n">
-        <v>96398</v>
+        <v>96411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -4017,7 +4017,7 @@
         <v>130076638</v>
       </c>
       <c r="B31" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>130076628</v>
       </c>
       <c r="B32" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>130076603</v>
       </c>
       <c r="B33" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>130076614</v>
       </c>
       <c r="B34" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>130076611</v>
       </c>
       <c r="B35" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -4017,7 +4017,7 @@
         <v>130076638</v>
       </c>
       <c r="B31" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>130076628</v>
       </c>
       <c r="B32" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>130076603</v>
       </c>
       <c r="B33" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>130076614</v>
       </c>
       <c r="B34" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>130076611</v>
       </c>
       <c r="B35" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60440-2024 artfynd.xlsx
+++ b/artfynd/A 60440-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74128624</v>
+        <v>121748695</v>
       </c>
       <c r="B2" t="n">
-        <v>98573</v>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2 Fiskartorpsholmen 1 km SV, Sm</t>
+          <t>Vinö, väst, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592966</v>
+        <v>593026</v>
       </c>
       <c r="R2" t="n">
-        <v>6417737</v>
+        <v>6417534</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G3j 3802. SOM: Corallorhiza trifida. LEG: Ingemar Hultgren</t>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,75 +775,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kärr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74573427</v>
+        <v>121748655</v>
       </c>
       <c r="B3" t="n">
-        <v>109316</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östanvik, vid vägskäl 700 m V, Sm</t>
+          <t>Vinö, väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592865</v>
+        <v>592998</v>
       </c>
       <c r="R3" t="n">
-        <v>6417736</v>
+        <v>6417689</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +863,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G3j 3801. SOM: Leontodon hispidus. LEG: Ingemar Hultgren</t>
+          <t>Stora kuddar i hela området!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,70 +892,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74969372</v>
+        <v>121748675</v>
       </c>
       <c r="B4" t="n">
-        <v>109528</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>22 Fiskartorpsholmen 1,1 km SV, Sm</t>
+          <t>Vinö, väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592865</v>
+        <v>593020</v>
       </c>
       <c r="R4" t="n">
-        <v>6417736</v>
+        <v>6417596</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,17 +980,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G3j 3801. SOM: Scorzonera humilis. LEG: Ingemar Hultgren</t>
+          <t>Flera stora. ca 1 m i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,37 +1009,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121738401</v>
+        <v>129278881</v>
       </c>
       <c r="B5" t="n">
-        <v>105262</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,49 +1039,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vinö öst, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592944</v>
+        <v>592953</v>
       </c>
       <c r="R5" t="n">
-        <v>6417875</v>
+        <v>6417881</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121748855</v>
+        <v>130076603</v>
       </c>
       <c r="B6" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,48 +1141,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vinö, väst, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593028</v>
+        <v>593101</v>
       </c>
       <c r="R6" t="n">
-        <v>6417470</v>
+        <v>6417299</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,12 +1199,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,22 +1229,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121748746</v>
+        <v>130076611</v>
       </c>
       <c r="B7" t="n">
-        <v>91157</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,45 +1247,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vinö, väst, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593178</v>
+        <v>593100</v>
       </c>
       <c r="R7" t="n">
-        <v>6417363</v>
+        <v>6417400</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,22 +1305,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,7 +1319,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,22 +1330,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121748655</v>
+        <v>130076628</v>
       </c>
       <c r="B8" t="n">
-        <v>94929</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,14 +1372,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vinö, väst, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592998</v>
+        <v>593090</v>
       </c>
       <c r="R8" t="n">
-        <v>6417689</v>
+        <v>6417440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,27 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stora kuddar i hela området!</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,37 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121748660</v>
+        <v>121748746</v>
       </c>
       <c r="B9" t="n">
-        <v>90781</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1523,7 +1474,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1534,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592977</v>
+        <v>593178</v>
       </c>
       <c r="R9" t="n">
-        <v>6417717</v>
+        <v>6417363</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,15 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121748838</v>
+        <v>121748855</v>
       </c>
       <c r="B10" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,32 +1569,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1656,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593110</v>
+        <v>593028</v>
       </c>
       <c r="R10" t="n">
-        <v>6417399</v>
+        <v>6417470</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1719,15 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121748713</v>
+        <v>129118299</v>
       </c>
       <c r="B11" t="n">
-        <v>90781</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,26 +1678,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1766,14 +1709,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vinö, väst, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593004</v>
+        <v>593021</v>
       </c>
       <c r="R11" t="n">
-        <v>6417448</v>
+        <v>6417797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,22 +1743,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,50 +1769,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121748675</v>
+        <v>121748660</v>
       </c>
       <c r="B12" t="n">
-        <v>94929</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1887,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593020</v>
+        <v>592977</v>
       </c>
       <c r="R12" t="n">
-        <v>6417596</v>
+        <v>6417717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,11 +1868,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flera stora. ca 1 m i diameter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,15 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121749241</v>
+        <v>121748713</v>
       </c>
       <c r="B13" t="n">
-        <v>90781</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,13 +1941,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593026</v>
+        <v>593004</v>
       </c>
       <c r="R13" t="n">
-        <v>6417534</v>
+        <v>6417448</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,9 +1974,19 @@
           <t>2024-12-26</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,15 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121748695</v>
+        <v>121749241</v>
       </c>
       <c r="B14" t="n">
-        <v>89839</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,31 +2025,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2136,7 +2066,7 @@
         <v>6417534</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2163,19 +2093,9 @@
           <t>2024-12-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,15 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122493944</v>
+        <v>122493919</v>
       </c>
       <c r="B15" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,32 +2134,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2318,12 +2235,7 @@
         <v>122493939</v>
       </c>
       <c r="B16" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,12 +2344,7 @@
         <v>122493970</v>
       </c>
       <c r="B17" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2543,15 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122493919</v>
+        <v>130076614</v>
       </c>
       <c r="B18" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2480,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2590,11 +2492,11 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vinö hällmarkstallskog, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593094</v>
+        <v>593100</v>
       </c>
       <c r="R18" t="n">
         <v>6417400</v>
@@ -2624,12 +2526,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,7 +2540,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2650,44 +2551,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123482713</v>
+        <v>130076638</v>
       </c>
       <c r="B19" t="n">
-        <v>57692</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102623</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2695,27 +2591,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vinö hällmarkstallskog, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593116</v>
+        <v>593208</v>
       </c>
       <c r="R19" t="n">
-        <v>6417388</v>
+        <v>6417302</v>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2739,12 +2634,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,6 +2648,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2764,72 +2660,66 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123551545</v>
+        <v>129118195</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 60440, Vinö, Sm</t>
+          <t>A 64440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593008</v>
+        <v>592920</v>
       </c>
       <c r="R20" t="n">
-        <v>6418130</v>
+        <v>6417775</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2853,22 +2743,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2877,6 +2757,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2895,51 +2776,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123551593</v>
+        <v>129278899</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2947,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593041</v>
+        <v>593282</v>
       </c>
       <c r="R21" t="n">
-        <v>6418091</v>
+        <v>6417172</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2977,22 +2852,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,37 +2885,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129118195</v>
+        <v>129350252</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>92567</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3066,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592920</v>
+        <v>593351</v>
       </c>
       <c r="R22" t="n">
-        <v>6417775</v>
+        <v>6417345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3096,12 +2961,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3129,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129118299</v>
+        <v>129279083</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,21 +3015,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3162,12 +3037,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3175,13 +3051,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593021</v>
+        <v>592964</v>
       </c>
       <c r="R23" t="n">
-        <v>6417797</v>
+        <v>6417600</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3205,12 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,7 +3095,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3113,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129118244</v>
+        <v>121748838</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>5495</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,49 +3124,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>101410</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>Vinö, väst, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592920</v>
+        <v>593110</v>
       </c>
       <c r="R24" t="n">
-        <v>6417775</v>
+        <v>6417399</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3315,12 +3187,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,6 +3201,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3340,17 +3213,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129278899</v>
+        <v>122493944</v>
       </c>
       <c r="B25" t="n">
-        <v>92908</v>
+        <v>5495</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3358,45 +3231,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>101410</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>Vinö hällmarkstallskog, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593282</v>
+        <v>593094</v>
       </c>
       <c r="R25" t="n">
-        <v>6417172</v>
+        <v>6417400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3423,12 +3294,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,56 +3320,69 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129278881</v>
+        <v>102289592</v>
       </c>
       <c r="B26" t="n">
-        <v>96365</v>
+        <v>43518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>101509</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>Stora Sundsvägen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592953</v>
+        <v>592916</v>
       </c>
       <c r="R26" t="n">
-        <v>6417881</v>
+        <v>6417460</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3525,12 +3409,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,39 +3430,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Thomas Persson Vinnersten</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Thomas Persson Vinnersten</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129279083</v>
+        <v>123482713</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>58129</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3595,23 +3479,23 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>Vinö hällmarkstallskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592964</v>
+        <v>593116</v>
       </c>
       <c r="R27" t="n">
-        <v>6417600</v>
+        <v>6417388</v>
       </c>
       <c r="S27" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3635,12 +3519,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3667,32 +3551,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129278856</v>
+        <v>123551545</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3704,20 +3588,20 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>A 60440, Vinö, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592957</v>
+        <v>593008</v>
       </c>
       <c r="R28" t="n">
-        <v>6417858</v>
+        <v>6418130</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3744,12 +3628,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,10 +3670,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129350271</v>
+        <v>129118244</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593357</v>
+        <v>592920</v>
       </c>
       <c r="R29" t="n">
-        <v>6417338</v>
+        <v>6417775</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3853,22 +3747,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,32 +3779,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129350252</v>
+        <v>129278856</v>
       </c>
       <c r="B30" t="n">
-        <v>92246</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3928,12 +3812,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3941,13 +3826,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593351</v>
+        <v>592957</v>
       </c>
       <c r="R30" t="n">
-        <v>6417345</v>
+        <v>6417858</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3971,22 +3856,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3995,7 +3870,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4014,10 +3888,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130076638</v>
+        <v>129350271</v>
       </c>
       <c r="B31" t="n">
-        <v>91749</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4025,21 +3899,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4047,12 +3921,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4060,13 +3935,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593208</v>
+        <v>593357</v>
       </c>
       <c r="R31" t="n">
-        <v>6417302</v>
+        <v>6417338</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4090,12 +3965,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,7 +3989,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4116,17 +4000,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130076628</v>
+        <v>74128624</v>
       </c>
       <c r="B32" t="n">
-        <v>96516</v>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,41 +4018,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>2 Fiskartorpsholmen 1 km SV, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593090</v>
+        <v>592966</v>
       </c>
       <c r="R32" t="n">
-        <v>6417440</v>
+        <v>6417737</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,12 +4072,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G3j 3802. SOM: Corallorhiza trifida. LEG: Ingemar Hultgren</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,71 +4091,75 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kärr</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130076603</v>
+        <v>74573427</v>
       </c>
       <c r="B33" t="n">
-        <v>96516</v>
+        <v>109865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>220228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>Östanvik, vid vägskäl 700 m V, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593101</v>
+        <v>592865</v>
       </c>
       <c r="R33" t="n">
-        <v>6417299</v>
+        <v>6417736</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4294,17 +4183,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>Smålands flora 2007: KOO: 7G3j 3801. SOM: Leontodon hispidus. LEG: Ingemar Hultgren</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4319,22 +4208,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130076614</v>
+        <v>74969372</v>
       </c>
       <c r="B34" t="n">
-        <v>91749</v>
+        <v>110077</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4342,48 +4235,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 64440, Vinö, Sm</t>
+          <t>22 Fiskartorpsholmen 1,1 km SV, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593100</v>
+        <v>592865</v>
       </c>
       <c r="R34" t="n">
-        <v>6417400</v>
+        <v>6417736</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4407,12 +4289,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G3j 3801. SOM: Scorzonera humilis. LEG: Ingemar Hultgren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,48 +4314,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130076611</v>
+        <v>123551593</v>
       </c>
       <c r="B35" t="n">
-        <v>96516</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4478,10 +4377,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593100</v>
+        <v>593041</v>
       </c>
       <c r="R35" t="n">
-        <v>6417400</v>
+        <v>6418091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4508,12 +4407,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4522,6 +4431,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4533,10 +4443,236 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121738401</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vinö öst, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592944</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6417875</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>74781124</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2 Fiskartorpsholmen 1 km SV, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592966</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6417737</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G3j 3802. SOM: Polygala vulgaris. LEG: Ingemar Hultgren</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
